--- a/testData/Opencart_LoginData.xlsx
+++ b/testData/Opencart_LoginData.xlsx
@@ -1,86 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18036" windowHeight="4800"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>res</t>
+  </si>
+  <si>
+    <t>test@123</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
+    <t>lakshmi@yahoo.com</t>
+  </si>
+  <si>
+    <t>Laxmi</t>
+  </si>
+  <si>
+    <t>Invalid</t>
+  </si>
+  <si>
+    <t>laksh@yahoo.com</t>
+  </si>
+  <si>
+    <t>Lakshmi</t>
+  </si>
+  <si>
+    <t>laks@yahoo.com</t>
+  </si>
+  <si>
+    <t>xyz</t>
+  </si>
+  <si>
+    <t>abc123@gmail.com</t>
+  </si>
   <si>
     <t>username</t>
   </si>
   <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>res</t>
-  </si>
-  <si>
-    <t>lakshmi@yahoo.com</t>
-  </si>
-  <si>
-    <t>Lakshmi</t>
-  </si>
-  <si>
-    <t>Valid</t>
-  </si>
-  <si>
-    <t>laksh@yahoo.com</t>
-  </si>
-  <si>
-    <t>Laxmi</t>
-  </si>
-  <si>
-    <t>Invalid</t>
-  </si>
-  <si>
-    <t>laks@yahoo.com</t>
-  </si>
-  <si>
-    <t>xyz</t>
-  </si>
-  <si>
-    <t>test@123</t>
-  </si>
-  <si>
-    <t>abc123@gmail.com</t>
-  </si>
-  <si>
-    <t>password1234</t>
-  </si>
-  <si>
     <t>chalwaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>Password1234</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,24 +88,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="16"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -121,7 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -150,27 +134,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -203,7 +175,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -215,7 +187,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -262,23 +234,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -314,23 +269,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -483,101 +421,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.21875" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.21875" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="A4" r:id="rId2"/>
-    <hyperlink ref="A3" r:id="rId3"/>
-    <hyperlink ref="A5" r:id="rId4"/>
-    <hyperlink ref="B2" r:id="rId5" display="test@123"/>
-    <hyperlink ref="A6" r:id="rId6"/>
-    <hyperlink ref="B6" r:id="rId7"/>
-    <hyperlink ref="B7" r:id="rId8"/>
+    <hyperlink ref="A4" r:id="rId1"/>
+    <hyperlink ref="A5" r:id="rId2"/>
+    <hyperlink ref="B2" r:id="rId3" display="test@123"/>
+    <hyperlink ref="B6" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId9"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>